--- a/ERP Report/PICS/SR ELITE(S - I)/MT-04/Zero Report.xlsx
+++ b/ERP Report/PICS/SR ELITE(S - I)/MT-04/Zero Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026\Acadamic 2026-2027\Question Paper Pics -2026\SR ELITE\MT\SR ELITE (P - 1) NEET MODULE TEST - 4 PAPER (15-09-2026)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73218C9-2883-42CD-ABB2-4F8770F39669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA627078-6790-45F8-B620-3E621E5BB3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="146">
   <si>
     <t>Q_No</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Biological Classification</t>
   </si>
   <si>
-    <t>Two Kingdom Classification</t>
-  </si>
-  <si>
     <t>MCQ</t>
   </si>
   <si>
@@ -77,18 +74,12 @@
     <t>Kingdom Monera</t>
   </si>
   <si>
-    <t>Systems of Classification</t>
-  </si>
-  <si>
     <t>Matching</t>
   </si>
   <si>
     <t>Matching Type</t>
   </si>
   <si>
-    <t>Viruses, Viroids and Lichens</t>
-  </si>
-  <si>
     <t>A&amp;R</t>
   </si>
   <si>
@@ -104,9 +95,6 @@
     <t>Algae - Phaeophyceae</t>
   </si>
   <si>
-    <t>Algae - Cell Wall</t>
-  </si>
-  <si>
     <t>Kingdom Fungi</t>
   </si>
   <si>
@@ -116,24 +104,15 @@
     <t>Algae - Chlorophyceae</t>
   </si>
   <si>
-    <t>Algae - Alternation of Generations</t>
-  </si>
-  <si>
     <t>Kingdom Protista - Euglenoids</t>
   </si>
   <si>
     <t>Kingdom Protista - Slime Moulds</t>
   </si>
   <si>
-    <t>Kingdom Monera and Kingdom Animalia</t>
-  </si>
-  <si>
     <t>Five Kingdom Classification</t>
   </si>
   <si>
-    <t>Algae</t>
-  </si>
-  <si>
     <t>Numerical</t>
   </si>
   <si>
@@ -149,18 +128,9 @@
     <t>Kingdom Fungi - Basidiomycetes</t>
   </si>
   <si>
-    <t>Kingdom Monera - Cyanobacteria</t>
-  </si>
-  <si>
-    <t>Kingdom Protista - Chrysophytes</t>
-  </si>
-  <si>
     <t>Kingdom Plantae</t>
   </si>
   <si>
-    <t>Three Domain System</t>
-  </si>
-  <si>
     <t>Kingdom Animalia</t>
   </si>
   <si>
@@ -176,130 +146,331 @@
     <t>Structural Organisation in Animals</t>
   </si>
   <si>
-    <t>Cockroach</t>
-  </si>
-  <si>
-    <t>Transport of Gases</t>
-  </si>
-  <si>
-    <t>Respiratory Organs in Human</t>
-  </si>
-  <si>
     <t>Mechanism of Breathing</t>
   </si>
   <si>
-    <t>Exchange of Gases</t>
-  </si>
-  <si>
-    <t>Frog</t>
-  </si>
-  <si>
-    <t>Disorders of Respiratory System</t>
-  </si>
-  <si>
     <t>Regulation of Respiration</t>
   </si>
   <si>
-    <t>Respiratory Organs in Animals</t>
-  </si>
-  <si>
-    <t>Semiconductor Devices</t>
-  </si>
-  <si>
-    <t>p-n Junction Diode</t>
-  </si>
-  <si>
-    <t>Photodiode</t>
-  </si>
-  <si>
-    <t>Zener Diode</t>
-  </si>
-  <si>
-    <t>Solar Cell</t>
-  </si>
-  <si>
     <t>Digital Electronics and Logic Gates</t>
   </si>
   <si>
-    <t>Special Purpose p-n Junction Diodes</t>
-  </si>
-  <si>
-    <t>Diode as a Rectifier</t>
-  </si>
-  <si>
-    <t>Intrinsic and Extrinsic Semiconductors</t>
-  </si>
-  <si>
-    <t>Stoichiometry</t>
-  </si>
-  <si>
-    <t>Stoichiometric Calculations</t>
-  </si>
-  <si>
-    <t>Empirical and Molecular Formula</t>
-  </si>
-  <si>
-    <t>Problems Based on Chemical Equations</t>
-  </si>
-  <si>
-    <t>Equivalent Weight</t>
-  </si>
-  <si>
-    <t>Equivalent Weight and n-factor</t>
-  </si>
-  <si>
-    <t>Mole Concept - Molarity</t>
-  </si>
-  <si>
-    <t>Mole Concept - Mole Fraction</t>
-  </si>
-  <si>
-    <t>Oxidation State</t>
-  </si>
-  <si>
-    <t>Types of Redox Reactions - n-factor</t>
-  </si>
-  <si>
-    <t>Balancing of Redox Reactions</t>
-  </si>
-  <si>
-    <t>Types of Redox Reactions</t>
-  </si>
-  <si>
-    <t>Chemical Bonding and Molecular structure</t>
-  </si>
-  <si>
-    <t>VB Theory &amp; Hybridisation</t>
-  </si>
-  <si>
-    <t>Valency</t>
-  </si>
-  <si>
-    <t>Hybridisation</t>
-  </si>
-  <si>
-    <t>Fajan's Rules</t>
-  </si>
-  <si>
-    <t>Formal Charge Calculations</t>
-  </si>
-  <si>
-    <t>Ionic Bond and Covalent Bond</t>
-  </si>
-  <si>
-    <t>VB Theory</t>
-  </si>
-  <si>
-    <t>Lewis Representation - Exceptions to Octet Rule</t>
-  </si>
-  <si>
-    <t>Exceptions to Octet Rule</t>
-  </si>
-  <si>
-    <t>Types of Redox Reactions - Disproportionation</t>
-  </si>
-  <si>
-    <t>Ionic Bond</t>
+    <t>Kingdom System of Classification (Two Kingdom Classification)</t>
+  </si>
+  <si>
+    <t>Kingdom Monera - Archaebacteria</t>
+  </si>
+  <si>
+    <t>Systems of Classification (Artificial, Natural, Phylogenetic, Cytotaxonomy)</t>
+  </si>
+  <si>
+    <t>Viruses, Viroids, Prions and Lichens - Viruses</t>
+  </si>
+  <si>
+    <t>Kingdom Monera - Eubacteria (Chemosynthetic Autotrophic Bacteria)</t>
+  </si>
+  <si>
+    <t>Kingdom Monera - Eubacteria (Heterotrophic Bacteria and Reproduction)</t>
+  </si>
+  <si>
+    <t>Viruses, Viroids, Prions and Lichens - Viruses (Bacteriophage)</t>
+  </si>
+  <si>
+    <t>Kingdom Monera - Eubacteria (Mycoplasma)</t>
+  </si>
+  <si>
+    <t>Kingdom Protista - Dinoflagellates</t>
+  </si>
+  <si>
+    <t>Viruses, Viroids, Prions and Lichens - Viruses and Viroids</t>
+  </si>
+  <si>
+    <t>Algae - Chlorophyceae, Phaeophyceae and Rhodophyceae (Cell Wall)</t>
+  </si>
+  <si>
+    <t>Kingdom Fungi - Ascomycetes</t>
+  </si>
+  <si>
+    <t>Viruses, Viroids, Prions and Lichens - Lichens</t>
+  </si>
+  <si>
+    <t>Plant Life Cycles and Alternation of Generations</t>
+  </si>
+  <si>
+    <t>Kingdom Fungi - Phycomycetes, Ascomycetes, Basidiomycetes and Deuteromycetes</t>
+  </si>
+  <si>
+    <t>Five Kingdom Classification (Kingdom Monera and Kingdom Animalia)</t>
+  </si>
+  <si>
+    <t>Algae - Chlorophyceae, Phaeophyceae and Rhodophyceae (Flagella)</t>
+  </si>
+  <si>
+    <t>Algae - Rhodophyceae (Economic Importance)</t>
+  </si>
+  <si>
+    <t>Algae - Economic Importance of Algae</t>
+  </si>
+  <si>
+    <t>Kingdom Monera - Eubacteria (Cyanobacteria)</t>
+  </si>
+  <si>
+    <t>Kingdom Protista - Chrysophytes (Diatoms)</t>
+  </si>
+  <si>
+    <t>Algae - Characteristics and Economic Importance</t>
+  </si>
+  <si>
+    <t>Algae - Reproduction in Algae</t>
+  </si>
+  <si>
+    <t>Five Kingdom Classification (Three Domains of Life)</t>
+  </si>
+  <si>
+    <t>Viruses, Viroids, Prions and Lichens - Prions</t>
+  </si>
+  <si>
+    <t>Algae - Chlorophyceae (Pyrenoids)</t>
+  </si>
+  <si>
+    <t>Cockroach - Morphology (Thorax)</t>
+  </si>
+  <si>
+    <t>Transport of Gases - Transport of Carbon dioxide</t>
+  </si>
+  <si>
+    <t>Exchange of Gases (Partial Pressures of Gases)</t>
+  </si>
+  <si>
+    <t>Human Respiratory System (Alveoli)</t>
+  </si>
+  <si>
+    <t>Cockroach - Reproductive System</t>
+  </si>
+  <si>
+    <t>Cockroach - Anatomy (Excretory, Digestive and Reproductive System)</t>
+  </si>
+  <si>
+    <t>Exchange of Gases (Factors Affecting Diffusion)</t>
+  </si>
+  <si>
+    <t>Frog - Anatomy (Reproductive System)</t>
+  </si>
+  <si>
+    <t>Frog - Anatomy (Nervous System)</t>
+  </si>
+  <si>
+    <t>Human Respiratory System</t>
+  </si>
+  <si>
+    <t>Disorders of Respiratory System (Emphysema)</t>
+  </si>
+  <si>
+    <t>Frog - Anatomy (Digestive System)</t>
+  </si>
+  <si>
+    <t>Human Respiratory System (Conducting Part)</t>
+  </si>
+  <si>
+    <t>Frog - Reproductive System and Development</t>
+  </si>
+  <si>
+    <t>Frog - Morphology and Anatomy</t>
+  </si>
+  <si>
+    <t>Transport of Gases - Transport of Oxygen and Carbon dioxide</t>
+  </si>
+  <si>
+    <t>Frog - Anatomy (Circulatory System)</t>
+  </si>
+  <si>
+    <t>Cockroach - Digestive System</t>
+  </si>
+  <si>
+    <t>Transport of Gases - Transport of Oxygen</t>
+  </si>
+  <si>
+    <t>Cockroach - Morphology (Sexual Dimorphism)</t>
+  </si>
+  <si>
+    <t>Cockroach - Reproductive System (Ootheca)</t>
+  </si>
+  <si>
+    <t>Exchange of Gases (Diffusion Membrane)</t>
+  </si>
+  <si>
+    <t>Cockroach - Circulatory and Respiratory System</t>
+  </si>
+  <si>
+    <t>Cockroach - Morphology and Anatomy</t>
+  </si>
+  <si>
+    <t>Respiratory Organs</t>
+  </si>
+  <si>
+    <t>Frog - Anatomy (Digestive and Urogenital System)</t>
+  </si>
+  <si>
+    <t>Disorders of Respiratory System (Asthma and Emphysema)</t>
+  </si>
+  <si>
+    <t>Semiconductor Electronics: Materials, Devices and Simple Circuits</t>
+  </si>
+  <si>
+    <t>p-n Junction (Potential Barrier and Depletion Region)</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes - Photodiode</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes - Zener Diode</t>
+  </si>
+  <si>
+    <t>Semiconductor Diode (p-n Junction Diode under Forward Bias)</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes - Solar Cell</t>
+  </si>
+  <si>
+    <t>Semiconductor Diode (Diode Circuits)</t>
+  </si>
+  <si>
+    <t>Semiconductor Diode (p-n Junction Diode under Reverse Bias)</t>
+  </si>
+  <si>
+    <t>Semiconductor Diode (Dynamic Resistance)</t>
+  </si>
+  <si>
+    <t>Digital Electronics and Logic Gates (NOR Gate)</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes (Zener Diode, LED and Solar Cell)</t>
+  </si>
+  <si>
+    <t>Digital Electronics and Logic Gates (Combination of Gates)</t>
+  </si>
+  <si>
+    <t>p-n Junction (Depletion Region)</t>
+  </si>
+  <si>
+    <t>Digital Electronics and Logic Gates (NAND as Universal Gate)</t>
+  </si>
+  <si>
+    <t>Semiconductor Diode (V-I Characteristics and Dynamic Resistance)</t>
+  </si>
+  <si>
+    <t>p-n Junction (Potential Barrier)</t>
+  </si>
+  <si>
+    <t>Application of Junction Diode as a Rectifier (Full Wave Rectifier)</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes - Zener Diode as Voltage Regulator</t>
+  </si>
+  <si>
+    <t>Application of Junction Diode as a Rectifier (Half Wave Rectifier)</t>
+  </si>
+  <si>
+    <t>Application of Junction Diode as a Rectifier</t>
+  </si>
+  <si>
+    <t>Digital Electronics and Logic Gates (OR Gate)</t>
+  </si>
+  <si>
+    <t>Extrinsic Semiconductor (n-type and p-type Semiconductors)</t>
+  </si>
+  <si>
+    <t>p-n Junction (Diffusion and Drift Current)</t>
+  </si>
+  <si>
+    <t>Special Purpose p-n Junction Diodes (Solar Cell and LED)</t>
+  </si>
+  <si>
+    <t>Digital Electronics and Logic Gates (Boolean Expression)</t>
+  </si>
+  <si>
+    <t>Application of Junction Diode as a Rectifier (Filter)</t>
+  </si>
+  <si>
+    <t>Extrinsic Semiconductor (n-type Semiconductor)</t>
+  </si>
+  <si>
+    <t>Organic Chemistry - Some Basic Principles and Techniques</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Inductive Effect</t>
+  </si>
+  <si>
+    <t>Fundamental Concepts in Organic Reaction Mechanism (Fission of a Covalent Bond, Nucleophiles and Electrophiles)</t>
+  </si>
+  <si>
+    <t>Isomerism - Structural Isomerism</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Hyperconjugation</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Resonance Effect (Acidic Character)</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds</t>
+  </si>
+  <si>
+    <t>Fission of a Covalent Bond - Carbocations (Reactive Intermediates)</t>
+  </si>
+  <si>
+    <t>Isomerism - Stereoisomerism (Optical and Geometrical Isomerism)</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Resonance Structure</t>
+  </si>
+  <si>
+    <t>Isomerism - Stereoisomerism (Optical Isomerism)</t>
+  </si>
+  <si>
+    <t>Isomerism - Structural Isomerism (Functional and Metamerism)</t>
+  </si>
+  <si>
+    <t>Isomerism - Stereoisomerism (Geometrical Isomerism, E and Z)</t>
+  </si>
+  <si>
+    <t>Isomerism - Stereoisomerism (Cahn-Ingold-Prelog Rules)</t>
+  </si>
+  <si>
+    <t>Isomerism - Structural Isomerism (Metamerism)</t>
+  </si>
+  <si>
+    <t>Isomerism - Structural Isomerism (Positional and Functional Isomerism)</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Electromeric Effect</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds - Inductive Effect (Acidic Character)</t>
+  </si>
+  <si>
+    <t>Fundamental Concepts in Organic Reaction Mechanism - Nucleophiles and Electrophiles</t>
+  </si>
+  <si>
+    <t>Electronic Displacement Effects in Covalent Bonds (Inductive and Mesomeric Effects)</t>
+  </si>
+  <si>
+    <t>Isomerism - Stereoisomerism (Geometrical Isomerism)</t>
+  </si>
+  <si>
+    <t>Fission of a Covalent Bond - Free Radicals (Reactive Intermediates)</t>
+  </si>
+  <si>
+    <t>Fission of a Covalent Bond - Homolytic Fission (Free Radical Substitution)</t>
+  </si>
+  <si>
+    <t>Isomerism - Structural Isomerism (Functional Isomerism)</t>
+  </si>
+  <si>
+    <t>Fission of a Covalent Bond - Carbanions (Reactive Intermediates)</t>
+  </si>
+  <si>
+    <t>Resonance Structure and Stereoisomerism (Geometrical Isomerism)</t>
   </si>
 </sst>
 </file>
@@ -714,13 +885,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -734,13 +905,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -751,16 +922,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -774,13 +945,13 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -794,13 +965,13 @@
         <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -814,13 +985,13 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -834,13 +1005,13 @@
         <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -854,13 +1025,13 @@
         <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -874,13 +1045,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -894,13 +1065,13 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -911,16 +1082,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -931,16 +1102,16 @@
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -954,13 +1125,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -971,16 +1142,16 @@
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -994,13 +1165,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1014,13 +1185,13 @@
         <v>9</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1031,16 +1202,16 @@
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1051,16 +1222,16 @@
         <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1074,13 +1245,13 @@
         <v>9</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,13 +1265,13 @@
         <v>9</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1114,13 +1285,13 @@
         <v>9</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1134,13 +1305,13 @@
         <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1154,13 +1325,13 @@
         <v>9</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1174,13 +1345,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1194,13 +1365,13 @@
         <v>9</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1214,13 +1385,13 @@
         <v>9</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1231,16 +1402,16 @@
         <v>8</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1251,16 +1422,16 @@
         <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1274,13 +1445,13 @@
         <v>9</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1291,16 +1462,16 @@
         <v>8</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1311,16 +1482,16 @@
         <v>8</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1334,13 +1505,13 @@
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1354,13 +1525,13 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1374,13 +1545,13 @@
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1394,13 +1565,13 @@
         <v>9</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1411,16 +1582,16 @@
         <v>8</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1434,13 +1605,13 @@
         <v>9</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1451,16 +1622,16 @@
         <v>8</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1474,13 +1645,13 @@
         <v>9</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1491,16 +1662,16 @@
         <v>8</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1514,13 +1685,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1534,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1554,13 +1725,13 @@
         <v>9</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1574,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1591,16 +1762,16 @@
         <v>8</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1608,19 +1779,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1628,19 +1799,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1648,19 +1819,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1668,19 +1839,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1688,19 +1859,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1708,19 +1879,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1728,19 +1899,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1748,19 +1919,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1768,19 +1939,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1788,19 +1959,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1808,19 +1979,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1828,19 +1999,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1848,19 +2019,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1868,19 +2039,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1888,19 +2059,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1908,19 +2079,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1928,19 +2099,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1948,19 +2119,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1968,19 +2139,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1988,19 +2159,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2008,19 +2179,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2028,19 +2199,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2048,19 +2219,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2068,19 +2239,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2088,19 +2259,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2108,19 +2279,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2128,19 +2299,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2148,19 +2319,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2168,19 +2339,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2188,19 +2359,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2208,19 +2379,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2228,19 +2399,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,19 +2419,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2268,19 +2439,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2288,19 +2459,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2308,19 +2479,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2328,19 +2499,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2348,19 +2519,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2368,19 +2539,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2388,19 +2559,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2408,19 +2579,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2428,19 +2599,19 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2448,19 +2619,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2468,19 +2639,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2488,19 +2659,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2511,16 +2682,16 @@
         <v>6</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2531,16 +2702,16 @@
         <v>6</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2551,16 +2722,16 @@
         <v>6</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2571,16 +2742,16 @@
         <v>6</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,16 +2762,16 @@
         <v>6</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2611,16 +2782,16 @@
         <v>6</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2631,16 +2802,16 @@
         <v>6</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2651,16 +2822,16 @@
         <v>6</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2671,16 +2842,16 @@
         <v>6</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2691,16 +2862,16 @@
         <v>6</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2711,16 +2882,16 @@
         <v>6</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2731,16 +2902,16 @@
         <v>6</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2751,16 +2922,16 @@
         <v>6</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2771,16 +2942,16 @@
         <v>6</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2791,16 +2962,16 @@
         <v>6</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2811,16 +2982,16 @@
         <v>6</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2831,16 +3002,16 @@
         <v>6</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2851,16 +3022,16 @@
         <v>6</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2871,16 +3042,16 @@
         <v>6</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2891,16 +3062,16 @@
         <v>6</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2911,16 +3082,16 @@
         <v>6</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2931,16 +3102,16 @@
         <v>6</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2951,16 +3122,16 @@
         <v>6</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2971,16 +3142,16 @@
         <v>6</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2991,16 +3162,16 @@
         <v>6</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3011,16 +3182,16 @@
         <v>6</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3031,16 +3202,16 @@
         <v>6</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3051,16 +3222,16 @@
         <v>6</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3071,16 +3242,16 @@
         <v>6</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3091,16 +3262,16 @@
         <v>6</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3111,16 +3282,16 @@
         <v>6</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3131,16 +3302,16 @@
         <v>6</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3151,16 +3322,16 @@
         <v>6</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3171,16 +3342,16 @@
         <v>6</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3191,16 +3362,16 @@
         <v>6</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3211,16 +3382,16 @@
         <v>6</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3231,16 +3402,16 @@
         <v>6</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3251,16 +3422,16 @@
         <v>6</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3271,16 +3442,16 @@
         <v>6</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3291,16 +3462,16 @@
         <v>6</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3311,16 +3482,16 @@
         <v>6</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3331,16 +3502,16 @@
         <v>6</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3351,16 +3522,16 @@
         <v>6</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3371,16 +3542,16 @@
         <v>6</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3391,16 +3562,16 @@
         <v>6</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3411,16 +3582,16 @@
         <v>7</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3431,16 +3602,16 @@
         <v>7</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3451,16 +3622,16 @@
         <v>7</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3471,16 +3642,16 @@
         <v>7</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3491,16 +3662,16 @@
         <v>7</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3511,16 +3682,16 @@
         <v>7</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3531,16 +3702,16 @@
         <v>7</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3551,16 +3722,16 @@
         <v>7</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3571,16 +3742,16 @@
         <v>7</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3591,16 +3762,16 @@
         <v>7</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3611,16 +3782,16 @@
         <v>7</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,16 +3802,16 @@
         <v>7</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3651,16 +3822,16 @@
         <v>7</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3671,16 +3842,16 @@
         <v>7</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3691,16 +3862,16 @@
         <v>7</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3711,16 +3882,16 @@
         <v>7</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3731,16 +3902,16 @@
         <v>7</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3751,16 +3922,16 @@
         <v>7</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,16 +3942,16 @@
         <v>7</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3791,16 +3962,16 @@
         <v>7</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3811,16 +3982,16 @@
         <v>7</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3831,16 +4002,16 @@
         <v>7</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3851,16 +4022,16 @@
         <v>7</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3871,16 +4042,16 @@
         <v>7</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3891,16 +4062,16 @@
         <v>7</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3911,16 +4082,16 @@
         <v>7</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3931,16 +4102,16 @@
         <v>7</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3951,16 +4122,16 @@
         <v>7</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3971,16 +4142,16 @@
         <v>7</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3991,16 +4162,16 @@
         <v>7</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4011,16 +4182,16 @@
         <v>7</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4031,16 +4202,16 @@
         <v>7</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4051,16 +4222,16 @@
         <v>7</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4071,16 +4242,16 @@
         <v>7</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4091,16 +4262,16 @@
         <v>7</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,16 +4282,16 @@
         <v>7</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4131,16 +4302,16 @@
         <v>7</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4151,16 +4322,16 @@
         <v>7</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4171,16 +4342,16 @@
         <v>7</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4191,16 +4362,16 @@
         <v>7</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4211,16 +4382,16 @@
         <v>7</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4231,16 +4402,16 @@
         <v>7</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4251,16 +4422,16 @@
         <v>7</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4271,16 +4442,16 @@
         <v>7</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4291,16 +4462,16 @@
         <v>7</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
